--- a/document/ログイン機能.xlsx
+++ b/document/ログイン機能.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER122\Desktop\プロジェクト演習\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62522D99-4BD2-4DBD-A313-B66953AE1886}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{655AA7AB-6407-4A18-94F3-8CA2C9BE4802}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10140" yWindow="0" windowWidth="10455" windowHeight="10905" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -275,10 +275,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>タスク管理システム（以降TaskManと呼称する）にログインする。</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>ユーザーID・パスワードを入力フォームに入力し、成功するとメニュー画面に遷移する。</t>
     <rPh sb="13" eb="15">
       <t>ニュウリョク</t>
@@ -426,6 +422,13 @@
     <t>チームデジカレ</t>
     <phoneticPr fontId="8"/>
   </si>
+  <si>
+    <t>ログイン操作</t>
+    <rPh sb="4" eb="6">
+      <t>ソウサ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
 </sst>
 </file>
 
@@ -452,6 +455,7 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1290,29 +1294,86 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1332,77 +1393,23 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1422,10 +1429,16 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1449,17 +1462,17 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1467,29 +1480,20 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1715,85 +1719,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="78" t="s">
+      <c r="C2" s="79" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
-      <c r="J2" s="79"/>
-      <c r="K2" s="79"/>
-      <c r="L2" s="79"/>
-      <c r="M2" s="79"/>
-      <c r="N2" s="79"/>
-      <c r="O2" s="79"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="80"/>
+      <c r="G2" s="80"/>
+      <c r="H2" s="80"/>
+      <c r="I2" s="80"/>
+      <c r="J2" s="80"/>
+      <c r="K2" s="80"/>
+      <c r="L2" s="80"/>
+      <c r="M2" s="80"/>
+      <c r="N2" s="80"/>
+      <c r="O2" s="80"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="65"/>
-      <c r="K3" s="65"/>
-      <c r="L3" s="65"/>
-      <c r="M3" s="65"/>
-      <c r="N3" s="65"/>
-      <c r="O3" s="65"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="51"/>
+      <c r="L3" s="51"/>
+      <c r="M3" s="51"/>
+      <c r="N3" s="51"/>
+      <c r="O3" s="51"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
-      <c r="J4" s="65"/>
-      <c r="K4" s="65"/>
-      <c r="L4" s="65"/>
-      <c r="M4" s="65"/>
-      <c r="N4" s="65"/>
-      <c r="O4" s="65"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="51"/>
+      <c r="L4" s="51"/>
+      <c r="M4" s="51"/>
+      <c r="N4" s="51"/>
+      <c r="O4" s="51"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="65"/>
-      <c r="D5" s="65"/>
-      <c r="E5" s="65"/>
-      <c r="F5" s="65"/>
-      <c r="G5" s="65"/>
-      <c r="H5" s="65"/>
-      <c r="I5" s="65"/>
-      <c r="J5" s="65"/>
-      <c r="K5" s="65"/>
-      <c r="L5" s="65"/>
-      <c r="M5" s="65"/>
-      <c r="N5" s="65"/>
-      <c r="O5" s="65"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="51"/>
+      <c r="F5" s="51"/>
+      <c r="G5" s="51"/>
+      <c r="H5" s="51"/>
+      <c r="I5" s="51"/>
+      <c r="J5" s="51"/>
+      <c r="K5" s="51"/>
+      <c r="L5" s="51"/>
+      <c r="M5" s="51"/>
+      <c r="N5" s="51"/>
+      <c r="O5" s="51"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="65"/>
-      <c r="D6" s="65"/>
-      <c r="E6" s="65"/>
-      <c r="F6" s="65"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="65"/>
-      <c r="I6" s="65"/>
-      <c r="J6" s="65"/>
-      <c r="K6" s="65"/>
-      <c r="L6" s="65"/>
-      <c r="M6" s="65"/>
-      <c r="N6" s="65"/>
-      <c r="O6" s="65"/>
+      <c r="C6" s="51"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="51"/>
+      <c r="G6" s="51"/>
+      <c r="H6" s="51"/>
+      <c r="I6" s="51"/>
+      <c r="J6" s="51"/>
+      <c r="K6" s="51"/>
+      <c r="L6" s="51"/>
+      <c r="M6" s="51"/>
+      <c r="N6" s="51"/>
+      <c r="O6" s="51"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -1813,46 +1817,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="80" t="s">
+      <c r="E8" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="65"/>
-      <c r="G8" s="65"/>
-      <c r="H8" s="65"/>
-      <c r="I8" s="65"/>
-      <c r="J8" s="65"/>
-      <c r="K8" s="65"/>
-      <c r="L8" s="65"/>
-      <c r="M8" s="65"/>
+      <c r="F8" s="51"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="51"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="51"/>
+      <c r="K8" s="51"/>
+      <c r="L8" s="51"/>
+      <c r="M8" s="51"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="76" t="s">
+      <c r="G13" s="77" t="s">
         <v>2</v>
       </c>
-      <c r="H13" s="53"/>
-      <c r="I13" s="76" t="s">
+      <c r="H13" s="60"/>
+      <c r="I13" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="J13" s="55"/>
-      <c r="K13" s="53"/>
+      <c r="J13" s="42"/>
+      <c r="K13" s="60"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="76"/>
-      <c r="H14" s="53"/>
-      <c r="I14" s="76"/>
-      <c r="J14" s="55"/>
-      <c r="K14" s="53"/>
+      <c r="G14" s="77"/>
+      <c r="H14" s="60"/>
+      <c r="I14" s="77"/>
+      <c r="J14" s="42"/>
+      <c r="K14" s="60"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="76"/>
-      <c r="H15" s="53"/>
-      <c r="I15" s="76"/>
-      <c r="J15" s="55"/>
-      <c r="K15" s="53"/>
+      <c r="G15" s="77"/>
+      <c r="H15" s="60"/>
+      <c r="I15" s="77"/>
+      <c r="J15" s="42"/>
+      <c r="K15" s="60"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -1861,13 +1865,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="77" t="s">
+      <c r="G17" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="H17" s="65"/>
-      <c r="I17" s="65"/>
-      <c r="J17" s="65"/>
-      <c r="K17" s="65"/>
+      <c r="H17" s="51"/>
+      <c r="I17" s="51"/>
+      <c r="J17" s="51"/>
+      <c r="K17" s="51"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -2881,19 +2885,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="38" t="s">
+      <c r="B1" s="48"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="71" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="39"/>
-      <c r="F1" s="38" t="s">
+      <c r="E1" s="58"/>
+      <c r="F1" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="39"/>
+      <c r="G1" s="58"/>
       <c r="H1" s="5" t="s">
         <v>8</v>
       </c>
@@ -2905,192 +2909,192 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="64"/>
-      <c r="B2" s="65"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="40" t="s">
+      <c r="A2" s="50"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="72" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="41"/>
-      <c r="F2" s="40" t="s">
+      <c r="E2" s="73"/>
+      <c r="F2" s="72" t="s">
+        <v>78</v>
+      </c>
+      <c r="G2" s="73"/>
+      <c r="H2" s="76">
+        <v>46171</v>
+      </c>
+      <c r="I2" s="65" t="s">
+        <v>70</v>
+      </c>
+      <c r="J2" s="68"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="50"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="69"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1">
+      <c r="A4" s="53"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="70"/>
+    </row>
+    <row r="5" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A5" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="57"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="41" t="s">
         <v>79</v>
       </c>
-      <c r="G2" s="41"/>
-      <c r="H2" s="104">
-        <v>46171</v>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="43"/>
+    </row>
+    <row r="6" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A6" s="59" t="s">
+        <v>12</v>
       </c>
-      <c r="I2" s="46" t="s">
-        <v>70</v>
-      </c>
-      <c r="J2" s="49"/>
-    </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="64"/>
-      <c r="B3" s="65"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="50"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="66"/>
-      <c r="B4" s="67"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="51"/>
-    </row>
-    <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="68" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="69"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="56" t="s">
+      <c r="B6" s="42"/>
+      <c r="C6" s="60"/>
+      <c r="D6" s="41" t="s">
         <v>73</v>
       </c>
-      <c r="E5" s="55"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="55"/>
-      <c r="H5" s="55"/>
-      <c r="I5" s="55"/>
-      <c r="J5" s="57"/>
-    </row>
-    <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="54" t="s">
-        <v>12</v>
+      <c r="E6" s="42"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="42"/>
+      <c r="H6" s="42"/>
+      <c r="I6" s="42"/>
+      <c r="J6" s="43"/>
+    </row>
+    <row r="7" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A7" s="59" t="s">
+        <v>13</v>
       </c>
-      <c r="B6" s="55"/>
-      <c r="C6" s="53"/>
-      <c r="D6" s="56" t="s">
+      <c r="B7" s="42"/>
+      <c r="C7" s="60"/>
+      <c r="D7" s="41" t="s">
+        <v>71</v>
+      </c>
+      <c r="E7" s="42"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="42"/>
+      <c r="H7" s="42"/>
+      <c r="I7" s="42"/>
+      <c r="J7" s="43"/>
+    </row>
+    <row r="8" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A8" s="59" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="42"/>
+      <c r="C8" s="60"/>
+      <c r="D8" s="41" t="s">
+        <v>72</v>
+      </c>
+      <c r="E8" s="42"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="42"/>
+      <c r="I8" s="42"/>
+      <c r="J8" s="43"/>
+    </row>
+    <row r="9" spans="1:10" ht="79.5" customHeight="1">
+      <c r="A9" s="61" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="64" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="60"/>
+      <c r="D9" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="E6" s="55"/>
-      <c r="F6" s="55"/>
-      <c r="G6" s="55"/>
-      <c r="H6" s="55"/>
-      <c r="I6" s="55"/>
-      <c r="J6" s="57"/>
-    </row>
-    <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="54" t="s">
-        <v>13</v>
+      <c r="E9" s="42"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="42"/>
+      <c r="H9" s="42"/>
+      <c r="I9" s="42"/>
+      <c r="J9" s="43"/>
+    </row>
+    <row r="10" spans="1:10" ht="64.5" customHeight="1">
+      <c r="A10" s="62"/>
+      <c r="B10" s="64" t="s">
+        <v>17</v>
       </c>
-      <c r="B7" s="55"/>
-      <c r="C7" s="53"/>
-      <c r="D7" s="56" t="s">
-        <v>71</v>
-      </c>
-      <c r="E7" s="55"/>
-      <c r="F7" s="55"/>
-      <c r="G7" s="55"/>
-      <c r="H7" s="55"/>
-      <c r="I7" s="55"/>
-      <c r="J7" s="57"/>
-    </row>
-    <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="54" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="55"/>
-      <c r="C8" s="53"/>
-      <c r="D8" s="56" t="s">
-        <v>72</v>
-      </c>
-      <c r="E8" s="55"/>
-      <c r="F8" s="55"/>
-      <c r="G8" s="55"/>
-      <c r="H8" s="55"/>
-      <c r="I8" s="55"/>
-      <c r="J8" s="57"/>
-    </row>
-    <row r="9" spans="1:10" ht="79.5" customHeight="1">
-      <c r="A9" s="70" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="52" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="53"/>
-      <c r="D9" s="75" t="s">
+      <c r="C10" s="60"/>
+      <c r="D10" s="41" t="s">
         <v>75</v>
       </c>
-      <c r="E9" s="55"/>
-      <c r="F9" s="55"/>
-      <c r="G9" s="55"/>
-      <c r="H9" s="55"/>
-      <c r="I9" s="55"/>
-      <c r="J9" s="57"/>
-    </row>
-    <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="71"/>
-      <c r="B10" s="52" t="s">
-        <v>17</v>
+      <c r="E10" s="42"/>
+      <c r="F10" s="42"/>
+      <c r="G10" s="42"/>
+      <c r="H10" s="42"/>
+      <c r="I10" s="42"/>
+      <c r="J10" s="43"/>
+    </row>
+    <row r="11" spans="1:10" ht="153" customHeight="1">
+      <c r="A11" s="63"/>
+      <c r="B11" s="64" t="s">
+        <v>18</v>
       </c>
-      <c r="C10" s="53"/>
-      <c r="D10" s="56" t="s">
+      <c r="C11" s="60"/>
+      <c r="D11" s="44" t="s">
         <v>76</v>
       </c>
-      <c r="E10" s="55"/>
-      <c r="F10" s="55"/>
-      <c r="G10" s="55"/>
-      <c r="H10" s="55"/>
-      <c r="I10" s="55"/>
-      <c r="J10" s="57"/>
-    </row>
-    <row r="11" spans="1:10" ht="153" customHeight="1">
-      <c r="A11" s="72"/>
-      <c r="B11" s="52" t="s">
-        <v>18</v>
+      <c r="E11" s="42"/>
+      <c r="F11" s="42"/>
+      <c r="G11" s="42"/>
+      <c r="H11" s="42"/>
+      <c r="I11" s="42"/>
+      <c r="J11" s="43"/>
+    </row>
+    <row r="12" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A12" s="59" t="s">
+        <v>19</v>
       </c>
-      <c r="C11" s="53"/>
-      <c r="D11" s="75" t="s">
+      <c r="B12" s="42"/>
+      <c r="C12" s="60"/>
+      <c r="D12" s="41" t="s">
         <v>77</v>
       </c>
-      <c r="E11" s="55"/>
-      <c r="F11" s="55"/>
-      <c r="G11" s="55"/>
-      <c r="H11" s="55"/>
-      <c r="I11" s="55"/>
-      <c r="J11" s="57"/>
-    </row>
-    <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="54" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="55"/>
-      <c r="C12" s="53"/>
-      <c r="D12" s="56" t="s">
-        <v>78</v>
-      </c>
-      <c r="E12" s="55"/>
-      <c r="F12" s="55"/>
-      <c r="G12" s="55"/>
-      <c r="H12" s="55"/>
-      <c r="I12" s="55"/>
-      <c r="J12" s="57"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="42"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="43"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="58" t="s">
+      <c r="A13" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="59"/>
-      <c r="C13" s="60"/>
-      <c r="D13" s="73"/>
-      <c r="E13" s="59"/>
-      <c r="F13" s="59"/>
-      <c r="G13" s="59"/>
-      <c r="H13" s="59"/>
-      <c r="I13" s="59"/>
-      <c r="J13" s="74"/>
+      <c r="B13" s="39"/>
+      <c r="C13" s="46"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="39"/>
+      <c r="F13" s="39"/>
+      <c r="G13" s="39"/>
+      <c r="H13" s="39"/>
+      <c r="I13" s="39"/>
+      <c r="J13" s="40"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4081,6 +4085,25 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="D13:J13"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="D6:J6"/>
@@ -4089,25 +4112,6 @@
     <mergeCell ref="D9:J9"/>
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -4126,19 +4130,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="82" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="38" t="s">
+      <c r="B1" s="48"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="71" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="39"/>
-      <c r="F1" s="38" t="s">
+      <c r="E1" s="58"/>
+      <c r="F1" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="39"/>
+      <c r="G1" s="58"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -4150,40 +4154,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="64"/>
-      <c r="B2" s="65"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="49"/>
+      <c r="A2" s="50"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="68"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="64"/>
-      <c r="B3" s="65"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="50"/>
+      <c r="A3" s="50"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="69"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="66"/>
-      <c r="B4" s="67"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="51"/>
+      <c r="A4" s="53"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="70"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -5539,19 +5543,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="82" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="38" t="s">
+      <c r="B1" s="48"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="71" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="39"/>
-      <c r="F1" s="38" t="s">
+      <c r="E1" s="58"/>
+      <c r="F1" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="39"/>
+      <c r="G1" s="58"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -5563,44 +5567,44 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="64"/>
-      <c r="B2" s="65"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="40" t="s">
+      <c r="A2" s="50"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="72" t="s">
         <v>69</v>
       </c>
-      <c r="E2" s="41"/>
-      <c r="F2" s="40" t="s">
+      <c r="E2" s="73"/>
+      <c r="F2" s="72" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="41"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="49"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="68"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="64"/>
-      <c r="B3" s="65"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="50"/>
+      <c r="A3" s="50"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="69"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="66"/>
-      <c r="B4" s="67"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="51"/>
+      <c r="A4" s="53"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="70"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -6956,19 +6960,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="82" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="38" t="s">
+      <c r="B1" s="48"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="71" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="39"/>
-      <c r="F1" s="38" t="s">
+      <c r="E1" s="58"/>
+      <c r="F1" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="39"/>
+      <c r="G1" s="58"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -6980,40 +6984,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="64"/>
-      <c r="B2" s="65"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="49"/>
+      <c r="A2" s="50"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="68"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="64"/>
-      <c r="B3" s="65"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="50"/>
+      <c r="A3" s="50"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="69"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="66"/>
-      <c r="B4" s="67"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="51"/>
+      <c r="A4" s="53"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="70"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -8363,19 +8367,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="38" t="s">
+      <c r="B1" s="48"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="71" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="39"/>
-      <c r="F1" s="38" t="s">
+      <c r="E1" s="58"/>
+      <c r="F1" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="39"/>
+      <c r="G1" s="58"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -8387,189 +8391,189 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="64"/>
-      <c r="B2" s="65"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="49"/>
+      <c r="A2" s="50"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="68"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="64"/>
-      <c r="B3" s="65"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="50"/>
+      <c r="A3" s="50"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="69"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="64"/>
-      <c r="B4" s="65"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="42"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="50"/>
+      <c r="A4" s="50"/>
+      <c r="B4" s="51"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="74"/>
+      <c r="G4" s="52"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
+      <c r="J4" s="69"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="91" t="s">
+      <c r="A5" s="84" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="69"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="84"/>
-      <c r="E5" s="69"/>
-      <c r="F5" s="69"/>
-      <c r="G5" s="69"/>
-      <c r="H5" s="69"/>
-      <c r="I5" s="69"/>
-      <c r="J5" s="85"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="87"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="57"/>
+      <c r="H5" s="57"/>
+      <c r="I5" s="57"/>
+      <c r="J5" s="88"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="82" t="s">
+      <c r="A6" s="86" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="55"/>
-      <c r="C6" s="55"/>
-      <c r="D6" s="55"/>
-      <c r="E6" s="55"/>
-      <c r="F6" s="55"/>
-      <c r="G6" s="55"/>
-      <c r="H6" s="55"/>
-      <c r="I6" s="55"/>
-      <c r="J6" s="57"/>
+      <c r="B6" s="42"/>
+      <c r="C6" s="42"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="42"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="42"/>
+      <c r="H6" s="42"/>
+      <c r="I6" s="42"/>
+      <c r="J6" s="43"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="86"/>
-      <c r="B7" s="87"/>
-      <c r="C7" s="87"/>
-      <c r="D7" s="87"/>
-      <c r="E7" s="87"/>
-      <c r="F7" s="87"/>
-      <c r="G7" s="87"/>
-      <c r="H7" s="87"/>
-      <c r="I7" s="87"/>
-      <c r="J7" s="88"/>
+      <c r="A7" s="89"/>
+      <c r="B7" s="90"/>
+      <c r="C7" s="90"/>
+      <c r="D7" s="90"/>
+      <c r="E7" s="90"/>
+      <c r="F7" s="90"/>
+      <c r="G7" s="90"/>
+      <c r="H7" s="90"/>
+      <c r="I7" s="90"/>
+      <c r="J7" s="91"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="64"/>
-      <c r="B8" s="65"/>
-      <c r="C8" s="65"/>
-      <c r="D8" s="65"/>
-      <c r="E8" s="65"/>
-      <c r="F8" s="65"/>
-      <c r="G8" s="65"/>
-      <c r="H8" s="65"/>
-      <c r="I8" s="65"/>
-      <c r="J8" s="89"/>
+      <c r="A8" s="50"/>
+      <c r="B8" s="51"/>
+      <c r="C8" s="51"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="51"/>
+      <c r="F8" s="51"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="51"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="92"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="64"/>
-      <c r="B9" s="65"/>
-      <c r="C9" s="65"/>
-      <c r="D9" s="65"/>
-      <c r="E9" s="65"/>
-      <c r="F9" s="65"/>
-      <c r="G9" s="65"/>
-      <c r="H9" s="65"/>
-      <c r="I9" s="65"/>
-      <c r="J9" s="89"/>
+      <c r="A9" s="50"/>
+      <c r="B9" s="51"/>
+      <c r="C9" s="51"/>
+      <c r="D9" s="51"/>
+      <c r="E9" s="51"/>
+      <c r="F9" s="51"/>
+      <c r="G9" s="51"/>
+      <c r="H9" s="51"/>
+      <c r="I9" s="51"/>
+      <c r="J9" s="92"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="64"/>
-      <c r="B10" s="65"/>
-      <c r="C10" s="65"/>
-      <c r="D10" s="65"/>
-      <c r="E10" s="65"/>
-      <c r="F10" s="65"/>
-      <c r="G10" s="65"/>
-      <c r="H10" s="65"/>
-      <c r="I10" s="65"/>
-      <c r="J10" s="89"/>
+      <c r="A10" s="50"/>
+      <c r="B10" s="51"/>
+      <c r="C10" s="51"/>
+      <c r="D10" s="51"/>
+      <c r="E10" s="51"/>
+      <c r="F10" s="51"/>
+      <c r="G10" s="51"/>
+      <c r="H10" s="51"/>
+      <c r="I10" s="51"/>
+      <c r="J10" s="92"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="64"/>
-      <c r="B11" s="65"/>
-      <c r="C11" s="65"/>
-      <c r="D11" s="65"/>
-      <c r="E11" s="65"/>
-      <c r="F11" s="65"/>
-      <c r="G11" s="65"/>
-      <c r="H11" s="65"/>
-      <c r="I11" s="65"/>
-      <c r="J11" s="89"/>
+      <c r="A11" s="50"/>
+      <c r="B11" s="51"/>
+      <c r="C11" s="51"/>
+      <c r="D11" s="51"/>
+      <c r="E11" s="51"/>
+      <c r="F11" s="51"/>
+      <c r="G11" s="51"/>
+      <c r="H11" s="51"/>
+      <c r="I11" s="51"/>
+      <c r="J11" s="92"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="64"/>
-      <c r="B12" s="65"/>
-      <c r="C12" s="65"/>
-      <c r="D12" s="65"/>
-      <c r="E12" s="65"/>
-      <c r="F12" s="65"/>
-      <c r="G12" s="65"/>
-      <c r="H12" s="65"/>
-      <c r="I12" s="65"/>
-      <c r="J12" s="89"/>
+      <c r="A12" s="50"/>
+      <c r="B12" s="51"/>
+      <c r="C12" s="51"/>
+      <c r="D12" s="51"/>
+      <c r="E12" s="51"/>
+      <c r="F12" s="51"/>
+      <c r="G12" s="51"/>
+      <c r="H12" s="51"/>
+      <c r="I12" s="51"/>
+      <c r="J12" s="92"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="64"/>
-      <c r="B13" s="65"/>
-      <c r="C13" s="65"/>
-      <c r="D13" s="65"/>
-      <c r="E13" s="65"/>
-      <c r="F13" s="65"/>
-      <c r="G13" s="65"/>
-      <c r="H13" s="65"/>
-      <c r="I13" s="65"/>
-      <c r="J13" s="89"/>
+      <c r="A13" s="50"/>
+      <c r="B13" s="51"/>
+      <c r="C13" s="51"/>
+      <c r="D13" s="51"/>
+      <c r="E13" s="51"/>
+      <c r="F13" s="51"/>
+      <c r="G13" s="51"/>
+      <c r="H13" s="51"/>
+      <c r="I13" s="51"/>
+      <c r="J13" s="92"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="82" t="s">
+      <c r="A14" s="86" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="55"/>
-      <c r="C14" s="55"/>
-      <c r="D14" s="55"/>
-      <c r="E14" s="55"/>
-      <c r="F14" s="55"/>
-      <c r="G14" s="55"/>
-      <c r="H14" s="55"/>
-      <c r="I14" s="55"/>
-      <c r="J14" s="57"/>
+      <c r="B14" s="42"/>
+      <c r="C14" s="42"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="42"/>
+      <c r="F14" s="42"/>
+      <c r="G14" s="42"/>
+      <c r="H14" s="42"/>
+      <c r="I14" s="42"/>
+      <c r="J14" s="43"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="82" t="s">
+      <c r="A15" s="86" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="55"/>
-      <c r="C15" s="53"/>
-      <c r="D15" s="56"/>
-      <c r="E15" s="55"/>
-      <c r="F15" s="55"/>
-      <c r="G15" s="55"/>
-      <c r="H15" s="53"/>
+      <c r="B15" s="42"/>
+      <c r="C15" s="60"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="42"/>
+      <c r="F15" s="42"/>
+      <c r="G15" s="42"/>
+      <c r="H15" s="60"/>
       <c r="I15" s="15" t="s">
         <v>28</v>
       </c>
       <c r="J15" s="16"/>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="82" t="s">
+      <c r="A16" s="86" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="55"/>
-      <c r="C16" s="53"/>
+      <c r="B16" s="42"/>
+      <c r="C16" s="60"/>
       <c r="D16" s="15" t="s">
         <v>30</v>
       </c>
@@ -8582,95 +8586,95 @@
       <c r="G16" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="90" t="s">
+      <c r="H16" s="93" t="s">
         <v>20</v>
       </c>
-      <c r="I16" s="55"/>
-      <c r="J16" s="57"/>
+      <c r="I16" s="42"/>
+      <c r="J16" s="43"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
       <c r="A17" s="83"/>
-      <c r="B17" s="55"/>
-      <c r="C17" s="53"/>
+      <c r="B17" s="42"/>
+      <c r="C17" s="60"/>
       <c r="D17" s="17"/>
       <c r="E17" s="17"/>
       <c r="F17" s="18"/>
       <c r="G17" s="18"/>
-      <c r="H17" s="56"/>
-      <c r="I17" s="55"/>
-      <c r="J17" s="57"/>
+      <c r="H17" s="41"/>
+      <c r="I17" s="42"/>
+      <c r="J17" s="43"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
       <c r="A18" s="83"/>
-      <c r="B18" s="55"/>
-      <c r="C18" s="53"/>
+      <c r="B18" s="42"/>
+      <c r="C18" s="60"/>
       <c r="D18" s="17"/>
       <c r="E18" s="17"/>
       <c r="F18" s="18"/>
       <c r="G18" s="18"/>
-      <c r="H18" s="56"/>
-      <c r="I18" s="55"/>
-      <c r="J18" s="57"/>
+      <c r="H18" s="41"/>
+      <c r="I18" s="42"/>
+      <c r="J18" s="43"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
       <c r="A19" s="83"/>
-      <c r="B19" s="55"/>
-      <c r="C19" s="53"/>
+      <c r="B19" s="42"/>
+      <c r="C19" s="60"/>
       <c r="D19" s="17"/>
       <c r="E19" s="17"/>
       <c r="F19" s="18"/>
       <c r="G19" s="18"/>
-      <c r="H19" s="56"/>
-      <c r="I19" s="55"/>
-      <c r="J19" s="57"/>
+      <c r="H19" s="41"/>
+      <c r="I19" s="42"/>
+      <c r="J19" s="43"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
       <c r="A20" s="83"/>
-      <c r="B20" s="55"/>
-      <c r="C20" s="53"/>
+      <c r="B20" s="42"/>
+      <c r="C20" s="60"/>
       <c r="D20" s="17"/>
       <c r="E20" s="17"/>
       <c r="F20" s="18"/>
       <c r="G20" s="18"/>
-      <c r="H20" s="56"/>
-      <c r="I20" s="55"/>
-      <c r="J20" s="57"/>
+      <c r="H20" s="41"/>
+      <c r="I20" s="42"/>
+      <c r="J20" s="43"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
       <c r="A21" s="83"/>
-      <c r="B21" s="55"/>
-      <c r="C21" s="53"/>
+      <c r="B21" s="42"/>
+      <c r="C21" s="60"/>
       <c r="D21" s="17"/>
       <c r="E21" s="17"/>
       <c r="F21" s="18"/>
       <c r="G21" s="18"/>
-      <c r="H21" s="56"/>
-      <c r="I21" s="55"/>
-      <c r="J21" s="57"/>
+      <c r="H21" s="41"/>
+      <c r="I21" s="42"/>
+      <c r="J21" s="43"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
       <c r="A22" s="83"/>
-      <c r="B22" s="55"/>
-      <c r="C22" s="53"/>
+      <c r="B22" s="42"/>
+      <c r="C22" s="60"/>
       <c r="D22" s="17"/>
       <c r="E22" s="17"/>
       <c r="F22" s="18"/>
       <c r="G22" s="18"/>
-      <c r="H22" s="56"/>
-      <c r="I22" s="55"/>
-      <c r="J22" s="57"/>
+      <c r="H22" s="41"/>
+      <c r="I22" s="42"/>
+      <c r="J22" s="43"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="92"/>
-      <c r="B23" s="59"/>
-      <c r="C23" s="60"/>
+      <c r="A23" s="85"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="46"/>
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
       <c r="G23" s="20"/>
-      <c r="H23" s="73"/>
-      <c r="I23" s="59"/>
-      <c r="J23" s="74"/>
+      <c r="H23" s="38"/>
+      <c r="I23" s="39"/>
+      <c r="J23" s="40"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -9651,17 +9655,10 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
@@ -9678,10 +9675,17 @@
     <mergeCell ref="H16:J16"/>
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9700,182 +9704,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="63"/>
-      <c r="G1" s="38" t="s">
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="71" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="69"/>
-      <c r="I1" s="69"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="38" t="s">
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
+      <c r="J1" s="58"/>
+      <c r="K1" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="69"/>
-      <c r="M1" s="69"/>
-      <c r="N1" s="39"/>
-      <c r="O1" s="38" t="s">
+      <c r="L1" s="57"/>
+      <c r="M1" s="57"/>
+      <c r="N1" s="58"/>
+      <c r="O1" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="39"/>
-      <c r="Q1" s="38" t="s">
+      <c r="P1" s="58"/>
+      <c r="Q1" s="71" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="39"/>
-      <c r="S1" s="38" t="s">
+      <c r="R1" s="58"/>
+      <c r="S1" s="71" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="85"/>
+      <c r="T1" s="88"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="64"/>
-      <c r="B2" s="65"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="87"/>
-      <c r="I2" s="87"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="40"/>
-      <c r="L2" s="87"/>
-      <c r="M2" s="87"/>
-      <c r="N2" s="41"/>
-      <c r="O2" s="40"/>
-      <c r="P2" s="41"/>
-      <c r="Q2" s="40"/>
-      <c r="R2" s="41"/>
-      <c r="S2" s="40"/>
-      <c r="T2" s="88"/>
+      <c r="A2" s="50"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="90"/>
+      <c r="I2" s="90"/>
+      <c r="J2" s="73"/>
+      <c r="K2" s="72"/>
+      <c r="L2" s="90"/>
+      <c r="M2" s="90"/>
+      <c r="N2" s="73"/>
+      <c r="O2" s="72"/>
+      <c r="P2" s="73"/>
+      <c r="Q2" s="72"/>
+      <c r="R2" s="73"/>
+      <c r="S2" s="72"/>
+      <c r="T2" s="91"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="64"/>
-      <c r="B3" s="65"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="43"/>
-      <c r="K3" s="42"/>
-      <c r="L3" s="65"/>
-      <c r="M3" s="65"/>
-      <c r="N3" s="43"/>
-      <c r="O3" s="42"/>
-      <c r="P3" s="43"/>
-      <c r="Q3" s="42"/>
-      <c r="R3" s="43"/>
-      <c r="S3" s="42"/>
-      <c r="T3" s="89"/>
+      <c r="A3" s="50"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="52"/>
+      <c r="K3" s="74"/>
+      <c r="L3" s="51"/>
+      <c r="M3" s="51"/>
+      <c r="N3" s="52"/>
+      <c r="O3" s="74"/>
+      <c r="P3" s="52"/>
+      <c r="Q3" s="74"/>
+      <c r="R3" s="52"/>
+      <c r="S3" s="74"/>
+      <c r="T3" s="92"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="66"/>
-      <c r="B4" s="67"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="44"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="45"/>
-      <c r="K4" s="44"/>
-      <c r="L4" s="67"/>
-      <c r="M4" s="67"/>
-      <c r="N4" s="45"/>
-      <c r="O4" s="44"/>
-      <c r="P4" s="45"/>
-      <c r="Q4" s="44"/>
-      <c r="R4" s="45"/>
-      <c r="S4" s="44"/>
-      <c r="T4" s="97"/>
+      <c r="A4" s="53"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="75"/>
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="75"/>
+      <c r="L4" s="54"/>
+      <c r="M4" s="54"/>
+      <c r="N4" s="55"/>
+      <c r="O4" s="75"/>
+      <c r="P4" s="55"/>
+      <c r="Q4" s="75"/>
+      <c r="R4" s="55"/>
+      <c r="S4" s="75"/>
+      <c r="T4" s="103"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="91" t="s">
+      <c r="A5" s="84" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="69"/>
-      <c r="C5" s="69"/>
-      <c r="D5" s="69"/>
-      <c r="E5" s="69"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="98" t="s">
+      <c r="B5" s="57"/>
+      <c r="C5" s="57"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="100" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="69"/>
-      <c r="I5" s="69"/>
-      <c r="J5" s="69"/>
-      <c r="K5" s="69"/>
-      <c r="L5" s="69"/>
-      <c r="M5" s="69"/>
-      <c r="N5" s="69"/>
-      <c r="O5" s="69"/>
-      <c r="P5" s="69"/>
-      <c r="Q5" s="69"/>
-      <c r="R5" s="69"/>
-      <c r="S5" s="69"/>
-      <c r="T5" s="85"/>
+      <c r="H5" s="57"/>
+      <c r="I5" s="57"/>
+      <c r="J5" s="57"/>
+      <c r="K5" s="57"/>
+      <c r="L5" s="57"/>
+      <c r="M5" s="57"/>
+      <c r="N5" s="57"/>
+      <c r="O5" s="57"/>
+      <c r="P5" s="57"/>
+      <c r="Q5" s="57"/>
+      <c r="R5" s="57"/>
+      <c r="S5" s="57"/>
+      <c r="T5" s="88"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="82" t="s">
+      <c r="A6" s="86" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="55"/>
-      <c r="C6" s="55"/>
-      <c r="D6" s="55"/>
-      <c r="E6" s="55"/>
-      <c r="F6" s="53"/>
-      <c r="G6" s="56" t="s">
+      <c r="B6" s="42"/>
+      <c r="C6" s="42"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="42"/>
+      <c r="F6" s="60"/>
+      <c r="G6" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="55"/>
-      <c r="I6" s="55"/>
-      <c r="J6" s="55"/>
-      <c r="K6" s="55"/>
-      <c r="L6" s="55"/>
-      <c r="M6" s="55"/>
-      <c r="N6" s="55"/>
-      <c r="O6" s="55"/>
-      <c r="P6" s="55"/>
-      <c r="Q6" s="55"/>
-      <c r="R6" s="55"/>
-      <c r="S6" s="55"/>
-      <c r="T6" s="57"/>
+      <c r="H6" s="42"/>
+      <c r="I6" s="42"/>
+      <c r="J6" s="42"/>
+      <c r="K6" s="42"/>
+      <c r="L6" s="42"/>
+      <c r="M6" s="42"/>
+      <c r="N6" s="42"/>
+      <c r="O6" s="42"/>
+      <c r="P6" s="42"/>
+      <c r="Q6" s="42"/>
+      <c r="R6" s="42"/>
+      <c r="S6" s="42"/>
+      <c r="T6" s="43"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="82" t="s">
+      <c r="A7" s="86" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="55"/>
-      <c r="C7" s="55"/>
-      <c r="D7" s="55"/>
-      <c r="E7" s="55"/>
-      <c r="F7" s="53"/>
-      <c r="G7" s="56" t="s">
+      <c r="B7" s="42"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="42"/>
+      <c r="E7" s="42"/>
+      <c r="F7" s="60"/>
+      <c r="G7" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="H7" s="55"/>
-      <c r="I7" s="55"/>
-      <c r="J7" s="55"/>
-      <c r="K7" s="55"/>
-      <c r="L7" s="55"/>
-      <c r="M7" s="55"/>
-      <c r="N7" s="55"/>
-      <c r="O7" s="55"/>
-      <c r="P7" s="55"/>
-      <c r="Q7" s="55"/>
-      <c r="R7" s="55"/>
-      <c r="S7" s="55"/>
-      <c r="T7" s="57"/>
+      <c r="H7" s="42"/>
+      <c r="I7" s="42"/>
+      <c r="J7" s="42"/>
+      <c r="K7" s="42"/>
+      <c r="L7" s="42"/>
+      <c r="M7" s="42"/>
+      <c r="N7" s="42"/>
+      <c r="O7" s="42"/>
+      <c r="P7" s="42"/>
+      <c r="Q7" s="42"/>
+      <c r="R7" s="42"/>
+      <c r="S7" s="42"/>
+      <c r="T7" s="43"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -10074,37 +10078,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="82" t="s">
+      <c r="A15" s="86" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="53"/>
-      <c r="C15" s="101" t="s">
+      <c r="B15" s="60"/>
+      <c r="C15" s="102" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="53"/>
-      <c r="E15" s="90" t="s">
+      <c r="D15" s="60"/>
+      <c r="E15" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="F15" s="53"/>
-      <c r="G15" s="90" t="s">
+      <c r="F15" s="60"/>
+      <c r="G15" s="93" t="s">
         <v>48</v>
       </c>
-      <c r="H15" s="55"/>
-      <c r="I15" s="53"/>
-      <c r="J15" s="90" t="s">
+      <c r="H15" s="42"/>
+      <c r="I15" s="60"/>
+      <c r="J15" s="93" t="s">
         <v>49</v>
       </c>
-      <c r="K15" s="53"/>
-      <c r="L15" s="90" t="s">
+      <c r="K15" s="60"/>
+      <c r="L15" s="93" t="s">
         <v>50</v>
       </c>
-      <c r="M15" s="55"/>
-      <c r="N15" s="53"/>
-      <c r="O15" s="90" t="s">
+      <c r="M15" s="42"/>
+      <c r="N15" s="60"/>
+      <c r="O15" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="P15" s="55"/>
-      <c r="Q15" s="53"/>
+      <c r="P15" s="42"/>
+      <c r="Q15" s="60"/>
       <c r="R15" s="15" t="s">
         <v>52</v>
       </c>
@@ -10116,37 +10120,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="99">
+      <c r="A16" s="94">
         <v>1</v>
       </c>
-      <c r="B16" s="53"/>
-      <c r="C16" s="100" t="s">
+      <c r="B16" s="60"/>
+      <c r="C16" s="95" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="53"/>
-      <c r="E16" s="100" t="s">
+      <c r="D16" s="60"/>
+      <c r="E16" s="95" t="s">
         <v>56</v>
       </c>
-      <c r="F16" s="53"/>
-      <c r="G16" s="93" t="s">
+      <c r="F16" s="60"/>
+      <c r="G16" s="101" t="s">
         <v>57</v>
       </c>
-      <c r="H16" s="55"/>
-      <c r="I16" s="53"/>
-      <c r="J16" s="93" t="s">
+      <c r="H16" s="42"/>
+      <c r="I16" s="60"/>
+      <c r="J16" s="101" t="s">
         <v>58</v>
       </c>
-      <c r="K16" s="53"/>
-      <c r="L16" s="95" t="s">
+      <c r="K16" s="60"/>
+      <c r="L16" s="98" t="s">
         <v>59</v>
       </c>
-      <c r="M16" s="55"/>
-      <c r="N16" s="53"/>
-      <c r="O16" s="95" t="s">
+      <c r="M16" s="42"/>
+      <c r="N16" s="60"/>
+      <c r="O16" s="98" t="s">
         <v>60</v>
       </c>
-      <c r="P16" s="55"/>
-      <c r="Q16" s="53"/>
+      <c r="P16" s="42"/>
+      <c r="Q16" s="60"/>
       <c r="R16" s="33"/>
       <c r="S16" s="33"/>
       <c r="T16" s="34"/>
@@ -10158,37 +10162,37 @@
       <c r="Z16" s="35"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="99">
+      <c r="A17" s="94">
         <v>2</v>
       </c>
-      <c r="B17" s="53"/>
-      <c r="C17" s="100" t="s">
+      <c r="B17" s="60"/>
+      <c r="C17" s="95" t="s">
         <v>61</v>
       </c>
-      <c r="D17" s="53"/>
-      <c r="E17" s="100" t="s">
+      <c r="D17" s="60"/>
+      <c r="E17" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="F17" s="53"/>
-      <c r="G17" s="93" t="s">
+      <c r="F17" s="60"/>
+      <c r="G17" s="101" t="s">
         <v>63</v>
       </c>
-      <c r="H17" s="55"/>
-      <c r="I17" s="53"/>
-      <c r="J17" s="93" t="s">
+      <c r="H17" s="42"/>
+      <c r="I17" s="60"/>
+      <c r="J17" s="101" t="s">
         <v>64</v>
       </c>
-      <c r="K17" s="53"/>
-      <c r="L17" s="95" t="s">
+      <c r="K17" s="60"/>
+      <c r="L17" s="98" t="s">
         <v>65</v>
       </c>
-      <c r="M17" s="55"/>
-      <c r="N17" s="53"/>
-      <c r="O17" s="95" t="s">
+      <c r="M17" s="42"/>
+      <c r="N17" s="60"/>
+      <c r="O17" s="98" t="s">
         <v>66</v>
       </c>
-      <c r="P17" s="55"/>
-      <c r="Q17" s="53"/>
+      <c r="P17" s="42"/>
+      <c r="Q17" s="60"/>
       <c r="R17" s="33"/>
       <c r="S17" s="33"/>
       <c r="T17" s="34"/>
@@ -10200,23 +10204,23 @@
       <c r="Z17" s="35"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="99"/>
-      <c r="B18" s="53"/>
-      <c r="C18" s="100"/>
-      <c r="D18" s="53"/>
-      <c r="E18" s="100"/>
-      <c r="F18" s="53"/>
-      <c r="G18" s="93"/>
-      <c r="H18" s="55"/>
-      <c r="I18" s="53"/>
-      <c r="J18" s="93"/>
-      <c r="K18" s="53"/>
-      <c r="L18" s="95"/>
-      <c r="M18" s="55"/>
-      <c r="N18" s="53"/>
-      <c r="O18" s="95"/>
-      <c r="P18" s="55"/>
-      <c r="Q18" s="53"/>
+      <c r="A18" s="94"/>
+      <c r="B18" s="60"/>
+      <c r="C18" s="95"/>
+      <c r="D18" s="60"/>
+      <c r="E18" s="95"/>
+      <c r="F18" s="60"/>
+      <c r="G18" s="101"/>
+      <c r="H18" s="42"/>
+      <c r="I18" s="60"/>
+      <c r="J18" s="101"/>
+      <c r="K18" s="60"/>
+      <c r="L18" s="98"/>
+      <c r="M18" s="42"/>
+      <c r="N18" s="60"/>
+      <c r="O18" s="98"/>
+      <c r="P18" s="42"/>
+      <c r="Q18" s="60"/>
       <c r="R18" s="33"/>
       <c r="S18" s="33"/>
       <c r="T18" s="34"/>
@@ -10228,23 +10232,23 @@
       <c r="Z18" s="35"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="99"/>
-      <c r="B19" s="53"/>
-      <c r="C19" s="100"/>
-      <c r="D19" s="53"/>
-      <c r="E19" s="100"/>
-      <c r="F19" s="53"/>
-      <c r="G19" s="93"/>
-      <c r="H19" s="55"/>
-      <c r="I19" s="53"/>
-      <c r="J19" s="93"/>
-      <c r="K19" s="53"/>
-      <c r="L19" s="95"/>
-      <c r="M19" s="55"/>
-      <c r="N19" s="53"/>
-      <c r="O19" s="95"/>
-      <c r="P19" s="55"/>
-      <c r="Q19" s="53"/>
+      <c r="A19" s="94"/>
+      <c r="B19" s="60"/>
+      <c r="C19" s="95"/>
+      <c r="D19" s="60"/>
+      <c r="E19" s="95"/>
+      <c r="F19" s="60"/>
+      <c r="G19" s="101"/>
+      <c r="H19" s="42"/>
+      <c r="I19" s="60"/>
+      <c r="J19" s="101"/>
+      <c r="K19" s="60"/>
+      <c r="L19" s="98"/>
+      <c r="M19" s="42"/>
+      <c r="N19" s="60"/>
+      <c r="O19" s="98"/>
+      <c r="P19" s="42"/>
+      <c r="Q19" s="60"/>
       <c r="R19" s="33"/>
       <c r="S19" s="33"/>
       <c r="T19" s="34"/>
@@ -10256,23 +10260,23 @@
       <c r="Z19" s="35"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="99"/>
-      <c r="B20" s="53"/>
-      <c r="C20" s="100"/>
-      <c r="D20" s="53"/>
-      <c r="E20" s="100"/>
-      <c r="F20" s="53"/>
-      <c r="G20" s="93"/>
-      <c r="H20" s="55"/>
-      <c r="I20" s="53"/>
-      <c r="J20" s="93"/>
-      <c r="K20" s="53"/>
-      <c r="L20" s="95"/>
-      <c r="M20" s="55"/>
-      <c r="N20" s="53"/>
-      <c r="O20" s="95"/>
-      <c r="P20" s="55"/>
-      <c r="Q20" s="53"/>
+      <c r="A20" s="94"/>
+      <c r="B20" s="60"/>
+      <c r="C20" s="95"/>
+      <c r="D20" s="60"/>
+      <c r="E20" s="95"/>
+      <c r="F20" s="60"/>
+      <c r="G20" s="101"/>
+      <c r="H20" s="42"/>
+      <c r="I20" s="60"/>
+      <c r="J20" s="101"/>
+      <c r="K20" s="60"/>
+      <c r="L20" s="98"/>
+      <c r="M20" s="42"/>
+      <c r="N20" s="60"/>
+      <c r="O20" s="98"/>
+      <c r="P20" s="42"/>
+      <c r="Q20" s="60"/>
       <c r="R20" s="33"/>
       <c r="S20" s="33"/>
       <c r="T20" s="34"/>
@@ -10284,23 +10288,23 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="99"/>
-      <c r="B21" s="53"/>
-      <c r="C21" s="100"/>
-      <c r="D21" s="53"/>
-      <c r="E21" s="100"/>
-      <c r="F21" s="53"/>
-      <c r="G21" s="93"/>
-      <c r="H21" s="55"/>
-      <c r="I21" s="53"/>
-      <c r="J21" s="93"/>
-      <c r="K21" s="53"/>
-      <c r="L21" s="95"/>
-      <c r="M21" s="55"/>
-      <c r="N21" s="53"/>
-      <c r="O21" s="95"/>
-      <c r="P21" s="55"/>
-      <c r="Q21" s="53"/>
+      <c r="A21" s="94"/>
+      <c r="B21" s="60"/>
+      <c r="C21" s="95"/>
+      <c r="D21" s="60"/>
+      <c r="E21" s="95"/>
+      <c r="F21" s="60"/>
+      <c r="G21" s="101"/>
+      <c r="H21" s="42"/>
+      <c r="I21" s="60"/>
+      <c r="J21" s="101"/>
+      <c r="K21" s="60"/>
+      <c r="L21" s="98"/>
+      <c r="M21" s="42"/>
+      <c r="N21" s="60"/>
+      <c r="O21" s="98"/>
+      <c r="P21" s="42"/>
+      <c r="Q21" s="60"/>
       <c r="R21" s="33"/>
       <c r="S21" s="33"/>
       <c r="T21" s="34"/>
@@ -10312,23 +10316,23 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="99"/>
-      <c r="B22" s="53"/>
-      <c r="C22" s="100"/>
-      <c r="D22" s="53"/>
-      <c r="E22" s="100"/>
-      <c r="F22" s="53"/>
-      <c r="G22" s="93"/>
-      <c r="H22" s="55"/>
-      <c r="I22" s="53"/>
-      <c r="J22" s="93"/>
-      <c r="K22" s="53"/>
-      <c r="L22" s="95"/>
-      <c r="M22" s="55"/>
-      <c r="N22" s="53"/>
-      <c r="O22" s="95"/>
-      <c r="P22" s="55"/>
-      <c r="Q22" s="53"/>
+      <c r="A22" s="94"/>
+      <c r="B22" s="60"/>
+      <c r="C22" s="95"/>
+      <c r="D22" s="60"/>
+      <c r="E22" s="95"/>
+      <c r="F22" s="60"/>
+      <c r="G22" s="101"/>
+      <c r="H22" s="42"/>
+      <c r="I22" s="60"/>
+      <c r="J22" s="101"/>
+      <c r="K22" s="60"/>
+      <c r="L22" s="98"/>
+      <c r="M22" s="42"/>
+      <c r="N22" s="60"/>
+      <c r="O22" s="98"/>
+      <c r="P22" s="42"/>
+      <c r="Q22" s="60"/>
       <c r="R22" s="33"/>
       <c r="S22" s="33"/>
       <c r="T22" s="34"/>
@@ -10340,23 +10344,23 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="99"/>
-      <c r="B23" s="53"/>
-      <c r="C23" s="100"/>
-      <c r="D23" s="53"/>
-      <c r="E23" s="100"/>
-      <c r="F23" s="53"/>
-      <c r="G23" s="93"/>
-      <c r="H23" s="55"/>
-      <c r="I23" s="53"/>
-      <c r="J23" s="93"/>
-      <c r="K23" s="53"/>
-      <c r="L23" s="95"/>
-      <c r="M23" s="55"/>
-      <c r="N23" s="53"/>
-      <c r="O23" s="95"/>
-      <c r="P23" s="55"/>
-      <c r="Q23" s="53"/>
+      <c r="A23" s="94"/>
+      <c r="B23" s="60"/>
+      <c r="C23" s="95"/>
+      <c r="D23" s="60"/>
+      <c r="E23" s="95"/>
+      <c r="F23" s="60"/>
+      <c r="G23" s="101"/>
+      <c r="H23" s="42"/>
+      <c r="I23" s="60"/>
+      <c r="J23" s="101"/>
+      <c r="K23" s="60"/>
+      <c r="L23" s="98"/>
+      <c r="M23" s="42"/>
+      <c r="N23" s="60"/>
+      <c r="O23" s="98"/>
+      <c r="P23" s="42"/>
+      <c r="Q23" s="60"/>
       <c r="R23" s="33"/>
       <c r="S23" s="33"/>
       <c r="T23" s="34"/>
@@ -10368,23 +10372,23 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="99"/>
-      <c r="B24" s="53"/>
-      <c r="C24" s="100"/>
-      <c r="D24" s="53"/>
-      <c r="E24" s="100"/>
-      <c r="F24" s="53"/>
-      <c r="G24" s="93"/>
-      <c r="H24" s="55"/>
-      <c r="I24" s="53"/>
-      <c r="J24" s="93"/>
-      <c r="K24" s="53"/>
-      <c r="L24" s="95"/>
-      <c r="M24" s="55"/>
-      <c r="N24" s="53"/>
-      <c r="O24" s="95"/>
-      <c r="P24" s="55"/>
-      <c r="Q24" s="53"/>
+      <c r="A24" s="94"/>
+      <c r="B24" s="60"/>
+      <c r="C24" s="95"/>
+      <c r="D24" s="60"/>
+      <c r="E24" s="95"/>
+      <c r="F24" s="60"/>
+      <c r="G24" s="101"/>
+      <c r="H24" s="42"/>
+      <c r="I24" s="60"/>
+      <c r="J24" s="101"/>
+      <c r="K24" s="60"/>
+      <c r="L24" s="98"/>
+      <c r="M24" s="42"/>
+      <c r="N24" s="60"/>
+      <c r="O24" s="98"/>
+      <c r="P24" s="42"/>
+      <c r="Q24" s="60"/>
       <c r="R24" s="33"/>
       <c r="S24" s="33"/>
       <c r="T24" s="34"/>
@@ -10396,23 +10400,23 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="99"/>
-      <c r="B25" s="53"/>
-      <c r="C25" s="100"/>
-      <c r="D25" s="53"/>
-      <c r="E25" s="100"/>
-      <c r="F25" s="53"/>
-      <c r="G25" s="93"/>
-      <c r="H25" s="55"/>
-      <c r="I25" s="53"/>
-      <c r="J25" s="93"/>
-      <c r="K25" s="53"/>
-      <c r="L25" s="95"/>
-      <c r="M25" s="55"/>
-      <c r="N25" s="53"/>
-      <c r="O25" s="95"/>
-      <c r="P25" s="55"/>
-      <c r="Q25" s="53"/>
+      <c r="A25" s="94"/>
+      <c r="B25" s="60"/>
+      <c r="C25" s="95"/>
+      <c r="D25" s="60"/>
+      <c r="E25" s="95"/>
+      <c r="F25" s="60"/>
+      <c r="G25" s="101"/>
+      <c r="H25" s="42"/>
+      <c r="I25" s="60"/>
+      <c r="J25" s="101"/>
+      <c r="K25" s="60"/>
+      <c r="L25" s="98"/>
+      <c r="M25" s="42"/>
+      <c r="N25" s="60"/>
+      <c r="O25" s="98"/>
+      <c r="P25" s="42"/>
+      <c r="Q25" s="60"/>
       <c r="R25" s="33"/>
       <c r="S25" s="33"/>
       <c r="T25" s="34"/>
@@ -10424,23 +10428,23 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="99"/>
-      <c r="B26" s="53"/>
-      <c r="C26" s="100"/>
-      <c r="D26" s="53"/>
-      <c r="E26" s="100"/>
-      <c r="F26" s="53"/>
-      <c r="G26" s="93"/>
-      <c r="H26" s="55"/>
-      <c r="I26" s="53"/>
-      <c r="J26" s="93"/>
-      <c r="K26" s="53"/>
-      <c r="L26" s="95"/>
-      <c r="M26" s="55"/>
-      <c r="N26" s="53"/>
-      <c r="O26" s="95"/>
-      <c r="P26" s="55"/>
-      <c r="Q26" s="53"/>
+      <c r="A26" s="94"/>
+      <c r="B26" s="60"/>
+      <c r="C26" s="95"/>
+      <c r="D26" s="60"/>
+      <c r="E26" s="95"/>
+      <c r="F26" s="60"/>
+      <c r="G26" s="101"/>
+      <c r="H26" s="42"/>
+      <c r="I26" s="60"/>
+      <c r="J26" s="101"/>
+      <c r="K26" s="60"/>
+      <c r="L26" s="98"/>
+      <c r="M26" s="42"/>
+      <c r="N26" s="60"/>
+      <c r="O26" s="98"/>
+      <c r="P26" s="42"/>
+      <c r="Q26" s="60"/>
       <c r="R26" s="33"/>
       <c r="S26" s="33"/>
       <c r="T26" s="34"/>
@@ -10452,23 +10456,23 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="99"/>
-      <c r="B27" s="53"/>
-      <c r="C27" s="100"/>
-      <c r="D27" s="53"/>
-      <c r="E27" s="100"/>
-      <c r="F27" s="53"/>
-      <c r="G27" s="93"/>
-      <c r="H27" s="55"/>
-      <c r="I27" s="53"/>
-      <c r="J27" s="93"/>
-      <c r="K27" s="53"/>
-      <c r="L27" s="95"/>
-      <c r="M27" s="55"/>
-      <c r="N27" s="53"/>
-      <c r="O27" s="95"/>
-      <c r="P27" s="55"/>
-      <c r="Q27" s="53"/>
+      <c r="A27" s="94"/>
+      <c r="B27" s="60"/>
+      <c r="C27" s="95"/>
+      <c r="D27" s="60"/>
+      <c r="E27" s="95"/>
+      <c r="F27" s="60"/>
+      <c r="G27" s="101"/>
+      <c r="H27" s="42"/>
+      <c r="I27" s="60"/>
+      <c r="J27" s="101"/>
+      <c r="K27" s="60"/>
+      <c r="L27" s="98"/>
+      <c r="M27" s="42"/>
+      <c r="N27" s="60"/>
+      <c r="O27" s="98"/>
+      <c r="P27" s="42"/>
+      <c r="Q27" s="60"/>
       <c r="R27" s="33"/>
       <c r="S27" s="33"/>
       <c r="T27" s="34"/>
@@ -10480,23 +10484,23 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="99"/>
-      <c r="B28" s="53"/>
-      <c r="C28" s="100"/>
-      <c r="D28" s="53"/>
-      <c r="E28" s="100"/>
-      <c r="F28" s="53"/>
-      <c r="G28" s="93"/>
-      <c r="H28" s="55"/>
-      <c r="I28" s="53"/>
-      <c r="J28" s="93"/>
-      <c r="K28" s="53"/>
-      <c r="L28" s="95"/>
-      <c r="M28" s="55"/>
-      <c r="N28" s="53"/>
-      <c r="O28" s="95"/>
-      <c r="P28" s="55"/>
-      <c r="Q28" s="53"/>
+      <c r="A28" s="94"/>
+      <c r="B28" s="60"/>
+      <c r="C28" s="95"/>
+      <c r="D28" s="60"/>
+      <c r="E28" s="95"/>
+      <c r="F28" s="60"/>
+      <c r="G28" s="101"/>
+      <c r="H28" s="42"/>
+      <c r="I28" s="60"/>
+      <c r="J28" s="101"/>
+      <c r="K28" s="60"/>
+      <c r="L28" s="98"/>
+      <c r="M28" s="42"/>
+      <c r="N28" s="60"/>
+      <c r="O28" s="98"/>
+      <c r="P28" s="42"/>
+      <c r="Q28" s="60"/>
       <c r="R28" s="33"/>
       <c r="S28" s="33"/>
       <c r="T28" s="34"/>
@@ -10508,23 +10512,23 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="99"/>
-      <c r="B29" s="53"/>
-      <c r="C29" s="100"/>
-      <c r="D29" s="53"/>
-      <c r="E29" s="100"/>
-      <c r="F29" s="53"/>
-      <c r="G29" s="93"/>
-      <c r="H29" s="55"/>
-      <c r="I29" s="53"/>
-      <c r="J29" s="93"/>
-      <c r="K29" s="53"/>
-      <c r="L29" s="95"/>
-      <c r="M29" s="55"/>
-      <c r="N29" s="53"/>
-      <c r="O29" s="95"/>
-      <c r="P29" s="55"/>
-      <c r="Q29" s="53"/>
+      <c r="A29" s="94"/>
+      <c r="B29" s="60"/>
+      <c r="C29" s="95"/>
+      <c r="D29" s="60"/>
+      <c r="E29" s="95"/>
+      <c r="F29" s="60"/>
+      <c r="G29" s="101"/>
+      <c r="H29" s="42"/>
+      <c r="I29" s="60"/>
+      <c r="J29" s="101"/>
+      <c r="K29" s="60"/>
+      <c r="L29" s="98"/>
+      <c r="M29" s="42"/>
+      <c r="N29" s="60"/>
+      <c r="O29" s="98"/>
+      <c r="P29" s="42"/>
+      <c r="Q29" s="60"/>
       <c r="R29" s="33"/>
       <c r="S29" s="33"/>
       <c r="T29" s="34"/>
@@ -10536,23 +10540,23 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="99"/>
-      <c r="B30" s="53"/>
-      <c r="C30" s="100"/>
-      <c r="D30" s="53"/>
-      <c r="E30" s="100"/>
-      <c r="F30" s="53"/>
-      <c r="G30" s="93"/>
-      <c r="H30" s="55"/>
-      <c r="I30" s="53"/>
-      <c r="J30" s="93"/>
-      <c r="K30" s="53"/>
-      <c r="L30" s="95"/>
-      <c r="M30" s="55"/>
-      <c r="N30" s="53"/>
-      <c r="O30" s="95"/>
-      <c r="P30" s="55"/>
-      <c r="Q30" s="53"/>
+      <c r="A30" s="94"/>
+      <c r="B30" s="60"/>
+      <c r="C30" s="95"/>
+      <c r="D30" s="60"/>
+      <c r="E30" s="95"/>
+      <c r="F30" s="60"/>
+      <c r="G30" s="101"/>
+      <c r="H30" s="42"/>
+      <c r="I30" s="60"/>
+      <c r="J30" s="101"/>
+      <c r="K30" s="60"/>
+      <c r="L30" s="98"/>
+      <c r="M30" s="42"/>
+      <c r="N30" s="60"/>
+      <c r="O30" s="98"/>
+      <c r="P30" s="42"/>
+      <c r="Q30" s="60"/>
       <c r="R30" s="33"/>
       <c r="S30" s="33"/>
       <c r="T30" s="34"/>
@@ -10564,23 +10568,23 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="102"/>
-      <c r="B31" s="60"/>
-      <c r="C31" s="103"/>
-      <c r="D31" s="60"/>
-      <c r="E31" s="103"/>
-      <c r="F31" s="60"/>
-      <c r="G31" s="94"/>
-      <c r="H31" s="59"/>
-      <c r="I31" s="60"/>
-      <c r="J31" s="94"/>
-      <c r="K31" s="60"/>
-      <c r="L31" s="96"/>
-      <c r="M31" s="59"/>
-      <c r="N31" s="60"/>
-      <c r="O31" s="96"/>
-      <c r="P31" s="59"/>
-      <c r="Q31" s="60"/>
+      <c r="A31" s="96"/>
+      <c r="B31" s="46"/>
+      <c r="C31" s="97"/>
+      <c r="D31" s="46"/>
+      <c r="E31" s="97"/>
+      <c r="F31" s="46"/>
+      <c r="G31" s="104"/>
+      <c r="H31" s="39"/>
+      <c r="I31" s="46"/>
+      <c r="J31" s="104"/>
+      <c r="K31" s="46"/>
+      <c r="L31" s="99"/>
+      <c r="M31" s="39"/>
+      <c r="N31" s="46"/>
+      <c r="O31" s="99"/>
+      <c r="P31" s="39"/>
+      <c r="Q31" s="46"/>
       <c r="R31" s="36"/>
       <c r="S31" s="36"/>
       <c r="T31" s="37"/>
@@ -11578,6 +11582,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -11602,118 +11718,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
